--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mr.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T17:54:48+00:00</t>
+    <t>2026-08-27T18:01:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mr.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T18:01:55+00:00</t>
+    <t>2026-08-28T06:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
